--- a/Employee_Reports_wi52/Nishan Ekanayake Ekanayake Mudiyanselage Q0574.xlsx
+++ b/Employee_Reports_wi52/Nishan Ekanayake Ekanayake Mudiyanselage Q0574.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1350,11 +1350,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1399,11 +1399,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1448,11 +1448,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1485,11 +1485,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-388</v>
+        <v>-396</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1522,11 +1522,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-111</v>
+        <v>-119</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1571,11 +1571,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1620,11 +1620,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1657,11 +1657,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1694,11 +1694,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1731,11 +1731,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1780,11 +1780,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1795,41 +1795,41 @@
       <c r="K29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>25-Aug-2024</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>25-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="3" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>23-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>22-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>725</v>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7907</v>
+        <v>7899</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7895</v>
+        <v>7887</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7895</v>
+        <v>7887</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7941</v>
+        <v>7933</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
